--- a/Luban/Config/Datas/#HeroFightPropertyConfig.xlsx
+++ b/Luban/Config/Datas/#HeroFightPropertyConfig.xlsx
@@ -8,24 +8,33 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C34ECA28-E444-4C65-89E4-2130C536C204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F91158C-AC4A-494B-82E3-6BF973329C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6120" yWindow="10980" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="91">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -384,6 +393,10 @@
   </si>
   <si>
     <t>0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(list#sep=,),int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -727,7 +740,7 @@
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="4" width="14.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9" style="1"/>
+    <col min="5" max="5" width="15.375" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.25" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.5" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="17" width="9" style="1"/>
@@ -856,7 +869,7 @@
         <v>5</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>4</v>
